--- a/MotherBoard/CPL BCGA_FCU_STR.xlsx
+++ b/MotherBoard/CPL BCGA_FCU_STR.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026-04-16" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_06_13" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="130">
   <si>
     <t>Designator</t>
   </si>
@@ -55,6 +55,36 @@
     <t>Comment</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>178MU0002</t>
+  </si>
+  <si>
+    <t>CAP-TH_L5.8-W3.6-P5.0-D0.6</t>
+  </si>
+  <si>
+    <t>10.287mm</t>
+  </si>
+  <si>
+    <t>-18.669mm</t>
+  </si>
+  <si>
+    <t>12.787mm</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
     <t>Q2</t>
   </si>
   <si>
@@ -76,10 +106,13 @@
     <t>-2.418mm</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>-14.351mm</t>
+  </si>
+  <si>
+    <t>7.787mm</t>
   </si>
   <si>
     <t>Q3</t>
@@ -103,108 +136,156 @@
     <t>RES-TH_BD2.3-L6.5-P10.50-D0.5</t>
   </si>
   <si>
-    <t>18.161mm</t>
+    <t>23.622mm</t>
+  </si>
+  <si>
+    <t>-7.112mm</t>
+  </si>
+  <si>
+    <t>-1.862mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>18.034mm</t>
+  </si>
+  <si>
+    <t>-12.362mm</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>MF1/4W-100Ω±1% T</t>
+  </si>
+  <si>
+    <t>20.828mm</t>
+  </si>
+  <si>
+    <t>100Ω</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>16.002mm</t>
+  </si>
+  <si>
+    <t>-20.32mm</t>
+  </si>
+  <si>
+    <t>-25.57mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>Mini DC-DC Boost Step Up Converter</t>
+  </si>
+  <si>
+    <t>MINI DC-DC BOOST STEP UP CONVERTER</t>
+  </si>
+  <si>
+    <t>68.834mm</t>
+  </si>
+  <si>
+    <t>-20.701mm</t>
+  </si>
+  <si>
+    <t>77.851mm</t>
+  </si>
+  <si>
+    <t>CN1</t>
+  </si>
+  <si>
+    <t>A1501WR-S-8P</t>
+  </si>
+  <si>
+    <t>CONN-TH_A1501WR-S-8P</t>
+  </si>
+  <si>
+    <t>3.048mm</t>
+  </si>
+  <si>
+    <t>-19.177mm</t>
+  </si>
+  <si>
+    <t>4.872mm</t>
+  </si>
+  <si>
+    <t>-13.927mm</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>MF1/4W-1KΩ±1%T52</t>
+  </si>
+  <si>
+    <t>19.431mm</t>
+  </si>
+  <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>22.86mm</t>
+  </si>
+  <si>
+    <t>-15.07mm</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CC1H104MC1FD3F6C10MF</t>
+  </si>
+  <si>
+    <t>CAP-TH_L5.0-W2.5-P5.00-D1.0</t>
+  </si>
+  <si>
+    <t>10.033mm</t>
+  </si>
+  <si>
+    <t>-22.479mm</t>
+  </si>
+  <si>
+    <t>7.533mm</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>-25.654mm</t>
+  </si>
+  <si>
+    <t>12.533mm</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>ERS1VM471G16OT</t>
+  </si>
+  <si>
+    <t>CAP-TH_BD10.0-P5.00-D1.0-FD</t>
+  </si>
+  <si>
+    <t>52.197mm</t>
   </si>
   <si>
     <t>-6.858mm</t>
   </si>
   <si>
-    <t>-12.108mm</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>20.828mm</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>MF1/4W-100Ω±1% T</t>
-  </si>
-  <si>
-    <t>23.495mm</t>
-  </si>
-  <si>
-    <t>100Ω</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>14.859mm</t>
-  </si>
-  <si>
-    <t>-19.812mm</t>
-  </si>
-  <si>
-    <t>-25.062mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>Mini DC-DC Boost Step Up Converter</t>
-  </si>
-  <si>
-    <t>MINI DC-DC BOOST STEP UP CONVERTER</t>
-  </si>
-  <si>
-    <t>68.834mm</t>
-  </si>
-  <si>
-    <t>-20.701mm</t>
-  </si>
-  <si>
-    <t>77.851mm</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>CC1H104MC1FD3F6C10MF</t>
-  </si>
-  <si>
-    <t>CAP-TH_L5.0-W2.5-P5.00-D1.0</t>
-  </si>
-  <si>
-    <t>10.033mm</t>
-  </si>
-  <si>
-    <t>-22.479mm</t>
-  </si>
-  <si>
-    <t>7.533mm</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>-25.654mm</t>
-  </si>
-  <si>
-    <t>12.533mm</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>ERS1VM471G16OT</t>
-  </si>
-  <si>
-    <t>CAP-TH_BD10.0-P5.00-D1.0-FD</t>
-  </si>
-  <si>
-    <t>52.324mm</t>
-  </si>
-  <si>
     <t>-4.318mm</t>
   </si>
   <si>
@@ -214,9 +295,6 @@
     <t>C4</t>
   </si>
   <si>
-    <t>52.197mm</t>
-  </si>
-  <si>
     <t>-20.193mm</t>
   </si>
   <si>
@@ -256,6 +334,30 @@
     <t>-1.111mm</t>
   </si>
   <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>ESP32-C3 OLED</t>
+  </si>
+  <si>
+    <t>35.814mm</t>
+  </si>
+  <si>
+    <t>-15.621mm</t>
+  </si>
+  <si>
+    <t>-72.136mm</t>
+  </si>
+  <si>
+    <t>-4.191mm</t>
+  </si>
+  <si>
+    <t>44.704mm</t>
+  </si>
+  <si>
+    <t>-6.731mm</t>
+  </si>
+  <si>
     <t>TP1</t>
   </si>
   <si>
@@ -271,9 +373,6 @@
     <t>-25.951mm</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>TP2</t>
   </si>
   <si>
@@ -302,96 +401,6 @@
   </si>
   <si>
     <t>-10.978mm</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>178MU0002</t>
-  </si>
-  <si>
-    <t>CAP-TH_L5.8-W3.6-P5.0-D0.6</t>
-  </si>
-  <si>
-    <t>10.287mm</t>
-  </si>
-  <si>
-    <t>-18.669mm</t>
-  </si>
-  <si>
-    <t>7.787mm</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>-14.351mm</t>
-  </si>
-  <si>
-    <t>CN1</t>
-  </si>
-  <si>
-    <t>A1501WR-S-8P</t>
-  </si>
-  <si>
-    <t>CONN-TH_A1501WR-S-8P</t>
-  </si>
-  <si>
-    <t>3.048mm</t>
-  </si>
-  <si>
-    <t>-19.177mm</t>
-  </si>
-  <si>
-    <t>4.872mm</t>
-  </si>
-  <si>
-    <t>-13.927mm</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>MF1/4W-1KΩ±1%T52</t>
-  </si>
-  <si>
-    <t>17.653mm</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>20.32mm</t>
-  </si>
-  <si>
-    <t>-14.562mm</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>ESP32-C3 OLED</t>
-  </si>
-  <si>
-    <t>35.814mm</t>
-  </si>
-  <si>
-    <t>-15.621mm</t>
-  </si>
-  <si>
-    <t>-72.136mm</t>
-  </si>
-  <si>
-    <t>-4.191mm</t>
-  </si>
-  <si>
-    <t>44.704mm</t>
-  </si>
-  <si>
-    <t>-6.731mm</t>
   </si>
 </sst>
 </file>
@@ -768,13 +777,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="14" width="20" customWidth="1"/>
+    <col min="1" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -817,37 +826,40 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
       <c r="J2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="s">
         <v>21</v>
@@ -859,36 +871,39 @@
         <v>22</v>
       </c>
       <c r="N2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -897,39 +912,42 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M3" t="s">
         <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s">
         <v>32</v>
@@ -941,86 +959,92 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M4" t="s">
         <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
       </c>
       <c r="L5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M5" t="s">
         <v>22</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -1029,42 +1053,45 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M6" t="s">
         <v>22</v>
       </c>
       <c r="N6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
         <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -1079,62 +1106,68 @@
         <v>22</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="O7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
         <v>47</v>
       </c>
-      <c r="E8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" t="s">
-        <v>48</v>
-      </c>
       <c r="J8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
       </c>
       <c r="L8">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s">
         <v>22</v>
       </c>
       <c r="N8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>53</v>
@@ -1149,10 +1182,10 @@
         <v>54</v>
       </c>
       <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
         <v>55</v>
-      </c>
-      <c r="I9" t="s">
-        <v>54</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -1161,45 +1194,48 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M9" t="s">
         <v>22</v>
       </c>
       <c r="N9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -1211,80 +1247,86 @@
         <v>22</v>
       </c>
       <c r="N10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="O10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11">
+        <v>90</v>
+      </c>
+      <c r="M11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" t="s">
         <v>63</v>
       </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="O11" t="s">
         <v>63</v>
       </c>
-      <c r="G11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11">
-        <v>270</v>
-      </c>
-      <c r="M11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1299,36 +1341,39 @@
         <v>22</v>
       </c>
       <c r="N12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="O12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
         <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1343,36 +1388,39 @@
         <v>22</v>
       </c>
       <c r="N13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="O13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1381,139 +1429,148 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M14" t="s">
         <v>22</v>
       </c>
       <c r="N14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="O14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
         <v>84</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" t="s">
         <v>85</v>
       </c>
-      <c r="F15" t="s">
+      <c r="I15" t="s">
         <v>84</v>
       </c>
-      <c r="G15" t="s">
-        <v>85</v>
-      </c>
-      <c r="H15" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" t="s">
-        <v>85</v>
-      </c>
       <c r="J15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="s">
         <v>21</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>86</v>
       </c>
-      <c r="N15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>87</v>
       </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16">
+        <v>270</v>
+      </c>
+      <c r="M16" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s">
+        <v>92</v>
+      </c>
+      <c r="O16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
         <v>88</v>
       </c>
-      <c r="E16" t="s">
+      <c r="D17" t="s">
         <v>89</v>
-      </c>
-      <c r="F16" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" t="s">
-        <v>89</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" t="s">
-        <v>86</v>
-      </c>
-      <c r="N16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>94</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s">
         <v>94</v>
       </c>
       <c r="H17" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" t="s">
         <v>95</v>
       </c>
-      <c r="I17" t="s">
-        <v>96</v>
-      </c>
       <c r="J17">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K17" t="s">
         <v>21</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="s">
         <v>22</v>
@@ -1521,31 +1578,34 @@
       <c r="N17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="s">
         <v>97</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>98</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>99</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>100</v>
       </c>
-      <c r="E18" t="s">
-        <v>101</v>
-      </c>
       <c r="F18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" t="s">
         <v>100</v>
       </c>
-      <c r="G18" t="s">
-        <v>101</v>
-      </c>
       <c r="H18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I18" t="s">
         <v>101</v>
@@ -1557,42 +1617,45 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M18" t="s">
         <v>22</v>
       </c>
       <c r="N18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="O18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>103</v>
       </c>
       <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
         <v>98</v>
       </c>
-      <c r="C19" t="s">
-        <v>99</v>
-      </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
         <v>104</v>
       </c>
-      <c r="F19" t="s">
-        <v>100</v>
-      </c>
       <c r="G19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" t="s">
         <v>104</v>
       </c>
-      <c r="H19" t="s">
-        <v>102</v>
-      </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1601,177 +1664,189 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M19" t="s">
         <v>22</v>
       </c>
       <c r="N19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="O19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20">
+        <v>16</v>
+      </c>
+      <c r="K20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s">
         <v>108</v>
       </c>
-      <c r="E20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="O20" t="s">
         <v>108</v>
       </c>
-      <c r="G20" t="s">
-        <v>109</v>
-      </c>
-      <c r="H20" t="s">
-        <v>110</v>
-      </c>
-      <c r="I20" t="s">
-        <v>111</v>
-      </c>
-      <c r="J20">
-        <v>10</v>
-      </c>
-      <c r="K20" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20">
-        <v>90</v>
-      </c>
-      <c r="M20" t="s">
-        <v>86</v>
-      </c>
-      <c r="N20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="F21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G21" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="H21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I21" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="s">
         <v>21</v>
       </c>
       <c r="L21">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N21" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="O21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
         <v>116</v>
       </c>
-      <c r="B22" t="s">
-        <v>113</v>
-      </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I22" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="s">
         <v>21</v>
       </c>
       <c r="L22">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N22" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="O22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F23" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G23" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J23">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K23" t="s">
         <v>21</v>
@@ -1783,7 +1858,10 @@
         <v>22</v>
       </c>
       <c r="N23" t="s">
-        <v>120</v>
+        <v>125</v>
+      </c>
+      <c r="O23" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
